--- a/artfynd/A 61925-2025 artfynd.xlsx
+++ b/artfynd/A 61925-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130158615</v>
+        <v>130158618</v>
       </c>
       <c r="B2" t="n">
-        <v>56931</v>
+        <v>57738</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620939</v>
+        <v>620683</v>
       </c>
       <c r="R2" t="n">
-        <v>6657012</v>
+        <v>6656734</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hane som vilade i grantopp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130158618</v>
+        <v>130158615</v>
       </c>
       <c r="B3" t="n">
-        <v>57738</v>
+        <v>56931</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620683</v>
+        <v>620939</v>
       </c>
       <c r="R3" t="n">
-        <v>6656734</v>
+        <v>6657012</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hane som vilade i grantopp</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 61925-2025 artfynd.xlsx
+++ b/artfynd/A 61925-2025 artfynd.xlsx
@@ -877,7 +877,7 @@
         <v>130158620</v>
       </c>
       <c r="B4" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>130158619</v>
       </c>
       <c r="B5" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61925-2025 artfynd.xlsx
+++ b/artfynd/A 61925-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130158618</v>
       </c>
       <c r="B2" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130158615</v>
       </c>
       <c r="B3" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>130158620</v>
       </c>
       <c r="B4" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>130158619</v>
       </c>
       <c r="B5" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>130158617</v>
       </c>
       <c r="B6" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 61925-2025 artfynd.xlsx
+++ b/artfynd/A 61925-2025 artfynd.xlsx
@@ -877,7 +877,7 @@
         <v>130158620</v>
       </c>
       <c r="B4" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>130158619</v>
       </c>
       <c r="B5" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61925-2025 artfynd.xlsx
+++ b/artfynd/A 61925-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130158618</v>
       </c>
       <c r="B2" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130158615</v>
       </c>
       <c r="B3" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>130158620</v>
       </c>
       <c r="B4" t="n">
-        <v>97794</v>
+        <v>97820</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>130158619</v>
       </c>
       <c r="B5" t="n">
-        <v>97794</v>
+        <v>97820</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>130158617</v>
       </c>
       <c r="B6" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 61925-2025 artfynd.xlsx
+++ b/artfynd/A 61925-2025 artfynd.xlsx
@@ -877,7 +877,7 @@
         <v>130158620</v>
       </c>
       <c r="B4" t="n">
-        <v>97820</v>
+        <v>97821</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>130158619</v>
       </c>
       <c r="B5" t="n">
-        <v>97820</v>
+        <v>97821</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61925-2025 artfynd.xlsx
+++ b/artfynd/A 61925-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130158618</v>
+        <v>130158615</v>
       </c>
       <c r="B2" t="n">
-        <v>57849</v>
+        <v>57042</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620683</v>
+        <v>620939</v>
       </c>
       <c r="R2" t="n">
-        <v>6656734</v>
+        <v>6657012</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hane som vilade i grantopp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130158615</v>
+        <v>130158618</v>
       </c>
       <c r="B3" t="n">
-        <v>57042</v>
+        <v>57849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620939</v>
+        <v>620683</v>
       </c>
       <c r="R3" t="n">
-        <v>6657012</v>
+        <v>6656734</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hane som vilade i grantopp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,7 +877,7 @@
         <v>130158620</v>
       </c>
       <c r="B4" t="n">
-        <v>97821</v>
+        <v>97822</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>130158619</v>
       </c>
       <c r="B5" t="n">
-        <v>97821</v>
+        <v>97822</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
